--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_48.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_48.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>Musician?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SelfConfidence</t>
+          <t>Perfectionism</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.6769647130877625</v>
+        <v>-0.683129605663324</v>
       </c>
       <c r="C2">
-        <v>-1.191634279928518</v>
+        <v>0.0885353930516401</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1593278124319225</v>
+        <v>0.2163257294363916</v>
       </c>
       <c r="C3">
-        <v>-0.2510860923363682</v>
+        <v>0.2084660372594228</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>2.000289856379417</v>
+        <v>1.208536975373988</v>
       </c>
       <c r="C4">
-        <v>1.385137512056552</v>
+        <v>0.04171632778400319</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-1.28211105386979</v>
+        <v>-0.5161426750753824</v>
       </c>
       <c r="C5">
-        <v>-0.08426084724575872</v>
+        <v>0.6248003856121327</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.376617576017348</v>
+        <v>2.212148830794855</v>
       </c>
       <c r="C6">
-        <v>0.6103662837016594</v>
+        <v>0.9566014530265505</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.890801506837401</v>
+        <v>0.2674514230989978</v>
       </c>
       <c r="C7">
-        <v>-0.7027711777251482</v>
+        <v>1.216429618370118</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-2.031240995876663</v>
+        <v>-0.6103019148715726</v>
       </c>
       <c r="C8">
-        <v>-2.312186573876603</v>
+        <v>-0.1636144218319721</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-2.362773808520296</v>
+        <v>2.342858598736159</v>
       </c>
       <c r="C9">
-        <v>-2.512926804461592</v>
+        <v>0.4246817893687647</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.7170852765580069</v>
+        <v>-0.3634041591217644</v>
       </c>
       <c r="C10">
-        <v>-0.1465988280356229</v>
+        <v>0.08072584666150531</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-2.403413517324609</v>
+        <v>1.580401447711606</v>
       </c>
       <c r="C11">
-        <v>-2.298214198557542</v>
+        <v>0.416638566251161</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.4367712410911614</v>
+        <v>-0.1399182928286975</v>
       </c>
       <c r="C12">
-        <v>-1.495892994425542</v>
+        <v>-0.7098254198927267</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.371594396236659</v>
+        <v>0.2958548728889902</v>
       </c>
       <c r="C13">
-        <v>-1.142136379854632</v>
+        <v>0.352525241550094</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.2866213486396864</v>
+        <v>-0.650979995810786</v>
       </c>
       <c r="C14">
-        <v>0.2717931351145161</v>
+        <v>-0.1576341232329352</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.8787373760392141</v>
+        <v>0.3035518738685724</v>
       </c>
       <c r="C15">
-        <v>-1.681980098319222</v>
+        <v>1.553000802999435</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.596714153252816</v>
+        <v>0.1985309383706619</v>
       </c>
       <c r="C16">
-        <v>1.058630212601537</v>
+        <v>-0.2514308201987662</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.226014638879402</v>
+        <v>2.038218964111689</v>
       </c>
       <c r="C17">
-        <v>-0.5942067935482989</v>
+        <v>1.004273054936926</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.2557401335986075</v>
+        <v>-1.038296003726392</v>
       </c>
       <c r="C18">
-        <v>-1.532317118669309</v>
+        <v>-1.634233911157802</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.007727593795185</v>
+        <v>0.3681361259952955</v>
       </c>
       <c r="C19">
-        <v>-0.1109542851107254</v>
+        <v>-0.2694360953781261</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.3735491926353</v>
+        <v>1.868165841122424</v>
       </c>
       <c r="C20">
-        <v>2.187961107702626</v>
+        <v>1.048981863296892</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.652040259811729</v>
+        <v>0.2900852777567566</v>
       </c>
       <c r="C21">
-        <v>0.9428121173565032</v>
+        <v>2.038604038059334</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.1975490140706533</v>
+        <v>-0.7000178761620203</v>
       </c>
       <c r="C22">
-        <v>-0.7205429319631886</v>
+        <v>-0.5628675022636604</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9720893415103083</v>
+        <v>-0.2432025398966348</v>
       </c>
       <c r="C23">
-        <v>1.082131708366026</v>
+        <v>-0.02042256146768825</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.2244424861480399</v>
+        <v>0.518390609696224</v>
       </c>
       <c r="C24">
-        <v>0.2918859322697158</v>
+        <v>1.293012692843889</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.1814825989986224</v>
+        <v>0.0680829295440149</v>
       </c>
       <c r="C25">
-        <v>0.2662010668204122</v>
+        <v>0.4840207326988675</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.4069072338177196</v>
+        <v>0.2182247407811516</v>
       </c>
       <c r="C26">
-        <v>0.1639742432018986</v>
+        <v>0.6943964815864764</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.06887145796082152</v>
+        <v>0.9458749033109207</v>
       </c>
       <c r="C27">
-        <v>0.3022512563265273</v>
+        <v>-1.47160297435452</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-1.247753362671215</v>
+        <v>-1.231639249596063</v>
       </c>
       <c r="C28">
-        <v>-0.5472078725482923</v>
+        <v>1.167875118883927</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.5058560759579943</v>
+        <v>-1.068173167949544</v>
       </c>
       <c r="C29">
-        <v>0.327246943878565</v>
+        <v>-0.2589835474339223</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.910759795290696</v>
+        <v>-0.9448355735600931</v>
       </c>
       <c r="C30">
-        <v>0.5685292544845395</v>
+        <v>-1.404734871508271</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.072985776940407</v>
+        <v>2.502429294745822</v>
       </c>
       <c r="C31">
-        <v>1.749508554869831</v>
+        <v>0.04336083224199172</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.07650077269789674</v>
+        <v>-0.1399252057815894</v>
       </c>
       <c r="C32">
-        <v>0.1991994706017826</v>
+        <v>-0.6268982115613198</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.1593513690529729</v>
+        <v>1.11509681270684</v>
       </c>
       <c r="C33">
-        <v>-0.3373097216844021</v>
+        <v>-0.102750047463981</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.2040629582785973</v>
+        <v>-0.1324723393843523</v>
       </c>
       <c r="C34">
-        <v>-0.7784965735502318</v>
+        <v>0.06478467686639747</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.03511870216885844</v>
+        <v>-0.4436587752677653</v>
       </c>
       <c r="C35">
-        <v>-0.04647425781684335</v>
+        <v>-2.490255751935192</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.5444732499592347</v>
+        <v>0.4653194528015147</v>
       </c>
       <c r="C36">
-        <v>0.2386292449951312</v>
+        <v>-0.1832774109491365</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.5096929986288093</v>
+        <v>-1.119166164267352</v>
       </c>
       <c r="C37">
-        <v>-0.01292978605031722</v>
+        <v>-0.2488499131713017</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-1.868467187480664</v>
+        <v>-0.2436765191768116</v>
       </c>
       <c r="C38">
-        <v>-1.059009477473329</v>
+        <v>-0.09480348374948314</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.786442192592732</v>
+        <v>-0.4782819283046687</v>
       </c>
       <c r="C39">
-        <v>1.647901713036641</v>
+        <v>-1.71324412435083</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.634629553050632</v>
+        <v>-1.049441584622256</v>
       </c>
       <c r="C40">
-        <v>-0.1196014843004714</v>
+        <v>-0.9167673094072506</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.4032503417383104</v>
+        <v>-2.137045325307882</v>
       </c>
       <c r="C41">
-        <v>1.320221773965122</v>
+        <v>0.3159865617550731</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.246677678338606</v>
+        <v>-0.1459286474876399</v>
       </c>
       <c r="C42">
-        <v>0.5113907009577803</v>
+        <v>-0.2037769796851846</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.1421925218695772</v>
+        <v>1.229706779400113</v>
       </c>
       <c r="C43">
-        <v>-0.1495351894735286</v>
+        <v>-0.008264408475395946</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.2874347043999306</v>
+        <v>0.742867376911774</v>
       </c>
       <c r="C44">
-        <v>0.7773589208327479</v>
+        <v>-1.339677687413127</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.3734077013757121</v>
+        <v>-1.614456541260819</v>
       </c>
       <c r="C45">
-        <v>0.6838195485323777</v>
+        <v>-1.158311717414628</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.0437522370367936</v>
+        <v>-0.2179402375726443</v>
       </c>
       <c r="C46">
-        <v>0.7022585262764784</v>
+        <v>-0.01050826186841176</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.573120540859347</v>
+        <v>0.6432864428407484</v>
       </c>
       <c r="C47">
-        <v>0.6760833534739148</v>
+        <v>-0.1608256731353001</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.427834683121217</v>
+        <v>0.02118240063994638</v>
       </c>
       <c r="C48">
-        <v>1.049894390892586</v>
+        <v>-0.134708308847438</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.9572301528006268</v>
+        <v>1.773705106747226</v>
       </c>
       <c r="C49">
-        <v>1.61482613389731</v>
+        <v>0.6756700604466994</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.9863180989259354</v>
+        <v>0.2946396504938732</v>
       </c>
       <c r="C50">
-        <v>0.145411832360657</v>
+        <v>-0.1824374962370044</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>2.464108560907242</v>
+        <v>-2.430089485853252</v>
       </c>
       <c r="C51">
-        <v>-1.258465415359179</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-0.2336448352458655</v>
-      </c>
-      <c r="C52">
-        <v>-0.2547373319775244</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-0.3263724686117641</v>
-      </c>
-      <c r="C53">
-        <v>0.5263021170248771</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>1.528364588713717</v>
-      </c>
-      <c r="C54">
-        <v>1.115791407578589</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-1.209765610419191</v>
-      </c>
-      <c r="C55">
-        <v>-0.101706363715022</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-1.108407645466961</v>
-      </c>
-      <c r="C56">
-        <v>0.7151677103956107</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-0.7434658855593457</v>
-      </c>
-      <c r="C57">
-        <v>-1.597871607350947</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.05985208251471808</v>
-      </c>
-      <c r="C58">
-        <v>0.6536835335746781</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-0.06430433189909013</v>
-      </c>
-      <c r="C59">
-        <v>0.4995059045818817</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.09627541964426289</v>
-      </c>
-      <c r="C60">
-        <v>-2.659865886290245</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-0.09986221666721518</v>
-      </c>
-      <c r="C61">
-        <v>-0.5204319068103149</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>1.816938682109261</v>
-      </c>
-      <c r="C62">
-        <v>0.1891582694868602</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>-0.5410815518829091</v>
-      </c>
-      <c r="C63">
-        <v>0.9389831286677742</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-2.045459143525188</v>
-      </c>
-      <c r="C64">
-        <v>-0.5948820496130482</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.6192542858148112</v>
-      </c>
-      <c r="C65">
-        <v>0.6266749230433487</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>-0.222584109999183</v>
-      </c>
-      <c r="C66">
-        <v>0.9044524258182356</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>0.4196163954658292</v>
-      </c>
-      <c r="C67">
-        <v>-1.592730014239738</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-1.797430535658288</v>
-      </c>
-      <c r="C68">
-        <v>-0.9700341205459757</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-0.4944962838708086</v>
-      </c>
-      <c r="C69">
-        <v>-0.6148003524543855</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>0.127058053960061</v>
-      </c>
-      <c r="C70">
-        <v>-0.300754086388562</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>0.4169663021391459</v>
-      </c>
-      <c r="C71">
-        <v>-0.8720320715604463</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.9727232173045202</v>
-      </c>
-      <c r="C72">
-        <v>0.1235923537952921</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.1070358439933325</v>
-      </c>
-      <c r="C73">
-        <v>1.426179636730008</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-0.6787668160081909</v>
-      </c>
-      <c r="C74">
-        <v>-0.7802032519294797</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-0.2270729464499388</v>
-      </c>
-      <c r="C75">
-        <v>0.1595595454709065</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-0.4890535665345277</v>
-      </c>
-      <c r="C76">
-        <v>-0.5034555338855151</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>0.07628271087862711</v>
-      </c>
-      <c r="C77">
-        <v>1.368968458063292</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-0.3034672320163136</v>
-      </c>
-      <c r="C78">
-        <v>0.1068509444367245</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>-0.1334801802647543</v>
-      </c>
-      <c r="C79">
-        <v>-0.9356796570439735</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>-1.268958726949735</v>
-      </c>
-      <c r="C80">
-        <v>-0.4469905511858196</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.6785244287739376</v>
-      </c>
-      <c r="C81">
-        <v>-0.7066819986924566</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>-0.6244136084083408</v>
-      </c>
-      <c r="C82">
-        <v>0.171523854318485</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>0.5029536959811289</v>
-      </c>
-      <c r="C83">
-        <v>-0.5451689508356383</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>1.28636487488311</v>
-      </c>
-      <c r="C84">
-        <v>0.3529704202379179</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-0.3866404918903826</v>
-      </c>
-      <c r="C85">
-        <v>0.4989694849971882</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-0.8677843726118796</v>
-      </c>
-      <c r="C86">
-        <v>0.9182226311227575</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1.473316174839852</v>
-      </c>
-      <c r="C87">
-        <v>-0.1227526778224494</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>0.395018050523208</v>
-      </c>
-      <c r="C88">
-        <v>-0.3301266504984793</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-0.8697705702647812</v>
-      </c>
-      <c r="C89">
-        <v>-0.4424690585101871</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>0.5797027928763794</v>
-      </c>
-      <c r="C90">
-        <v>-0.4760376455890438</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>0.8013694330488806</v>
-      </c>
-      <c r="C91">
-        <v>0.9702245788941205</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-1.198440090625357</v>
-      </c>
-      <c r="C92">
-        <v>2.767872483055989E-05</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>2.080705138833381</v>
-      </c>
-      <c r="C93">
-        <v>-0.2944476219594083</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.2136536382654799</v>
-      </c>
-      <c r="C94">
-        <v>-0.06487492260920841</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>1.964564829033908</v>
-      </c>
-      <c r="C95">
-        <v>2.42069755115256</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>0.7998158882988974</v>
-      </c>
-      <c r="C96">
-        <v>-0.2037752079553231</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.7822618438899381</v>
-      </c>
-      <c r="C97">
-        <v>2.249584087314369</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-1.192067140852017</v>
-      </c>
-      <c r="C98">
-        <v>0.2297366460230836</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-1.225796435387182</v>
-      </c>
-      <c r="C99">
-        <v>-0.04611261741911205</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.04845510404008666</v>
-      </c>
-      <c r="C100">
-        <v>-3.868439078334725</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-0.2272757670923755</v>
-      </c>
-      <c r="C101">
-        <v>-0.2284865497298044</v>
+        <v>-0.07396380034694539</v>
       </c>
     </row>
   </sheetData>
